--- a/input/ES/parameters.xlsx
+++ b/input/ES/parameters.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10920"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pineapple/IdeaProjects/SimPathsEU_AUG/input/ES/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0F105DA-E651-3742-ABA9-6D61FB6AB4C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80E47751-52A5-044A-823D-6829587BAC6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="24440" yWindow="5440" windowWidth="20300" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -287,13 +287,13 @@
     <t>MAX_AGE_TO_STAY_IN_CONTINUOUS_EDUCATION</t>
   </si>
   <si>
-    <t>40</t>
-  </si>
-  <si>
     <t>MIN_AGE_LEAVE_PH</t>
   </si>
   <si>
     <t>MAX_AGE_ADULT_CHILD</t>
+  </si>
+  <si>
+    <t>80</t>
   </si>
 </sst>
 </file>
@@ -815,7 +815,7 @@
         <v>17</v>
       </c>
       <c r="B16">
-        <v>25</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
@@ -831,7 +831,7 @@
         <v>19</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
@@ -1012,7 +1012,7 @@
     </row>
     <row r="41" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B41">
         <v>18</v>
@@ -1020,7 +1020,7 @@
     </row>
     <row r="42" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B42">
         <v>45</v>

--- a/input/ES/parameters.xlsx
+++ b/input/ES/parameters.xlsx
@@ -683,7 +683,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B42"/>
+  <dimension ref="A1:B43"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="42.33203125" customWidth="1"/>
@@ -1024,6 +1024,16 @@
       </c>
       <c r="B42">
         <v>45</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>LABOUR_SUPPLY_ESTIMATION_PRICE_YEAR</t>
+        </is>
+      </c>
+      <c r="B43">
+        <v>2023</v>
       </c>
     </row>
   </sheetData>
